--- a/Databases/Database3/Output/2018/db3_2018_extracted.xlsx
+++ b/Databases/Database3/Output/2018/db3_2018_extracted.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="228">
   <si>
     <t>SurveyDate</t>
   </si>
@@ -517,9 +517,6 @@
     <t>L9U LL=FG RL=_</t>
   </si>
   <si>
-    <t>0 banded birds then none readable</t>
-  </si>
-  <si>
     <t>Of//RB:S//b</t>
   </si>
   <si>
@@ -568,7 +565,7 @@
     <t>S/LY:bf/LG (bf = light blue flag, no code); reported directly to bander</t>
   </si>
   <si>
-    <t>this is just one says here. One individual. Band/flag code:1) YX6, color: green, position: upper left". The "O" is for an orange band on the right leg, position: upper right.</t>
+    <t>YX6, color: green, position: upper left". The "O" is for an orange band on the right leg, position: upper right.</t>
   </si>
   <si>
     <t>S//BK:Bf(C63)//YB</t>
@@ -613,7 +610,7 @@
     <t>FW[VA],_:S,_</t>
   </si>
   <si>
-    <t>4 Unbanded, 1) Banded - FK[UN], _ : S, _</t>
+    <t>Banded - FK[UN], _ : S, _</t>
   </si>
   <si>
     <t>Left leg: Orange flag, upper yellow band, lower green band. Right leg: Upper silver USFWS band, lower Yellow band</t>
@@ -1036,7 +1033,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N121"/>
+  <dimension ref="A1:N120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -1967,45 +1964,42 @@
         <v>145</v>
       </c>
       <c r="M26">
-        <v>1</v>
-      </c>
-      <c r="N26" t="s">
-        <v>167</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="1">
-        <v>43136</v>
+        <v>43133</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E27">
-        <v>30.50892</v>
+        <v>29.99092</v>
       </c>
       <c r="F27">
-        <v>-81.4785</v>
+        <v>-85.502</v>
       </c>
       <c r="G27">
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I27" t="s">
-        <v>123</v>
-      </c>
-      <c r="L27" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="M27">
-        <v>16</v>
+        <v>1</v>
+      </c>
+      <c r="N27" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -2107,10 +2101,7 @@
         <v>124</v>
       </c>
       <c r="M30">
-        <v>1</v>
-      </c>
-      <c r="N30" t="s">
-        <v>170</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -2118,31 +2109,34 @@
         <v>43133</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E31">
-        <v>29.99092</v>
+        <v>28.05099</v>
       </c>
       <c r="F31">
-        <v>-85.502</v>
+        <v>-82.8197</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I31" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M31">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="N31" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -2174,42 +2168,42 @@
         <v>125</v>
       </c>
       <c r="M32">
-        <v>1</v>
-      </c>
-      <c r="N32" t="s">
-        <v>171</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="1">
-        <v>43133</v>
+        <v>43134</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C33" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D33" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E33">
-        <v>28.05099</v>
+        <v>25.70076</v>
       </c>
       <c r="F33">
-        <v>-82.8197</v>
+        <v>-80.1549</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M33">
-        <v>27</v>
+        <v>1</v>
+      </c>
+      <c r="N33" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -2381,10 +2375,7 @@
         <v>126</v>
       </c>
       <c r="M38">
-        <v>1</v>
-      </c>
-      <c r="N38" t="s">
-        <v>176</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -2401,13 +2392,13 @@
         <v>64</v>
       </c>
       <c r="E39">
-        <v>25.70076</v>
+        <v>25.70171</v>
       </c>
       <c r="F39">
-        <v>-80.1549</v>
+        <v>-80.1544</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" t="s">
         <v>96</v>
@@ -2416,39 +2407,42 @@
         <v>126</v>
       </c>
       <c r="M39">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="1">
-        <v>43134</v>
+        <v>43137</v>
       </c>
       <c r="B40" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C40" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D40" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E40">
-        <v>25.70171</v>
+        <v>29.071</v>
       </c>
       <c r="F40">
-        <v>-80.1544</v>
+        <v>-80.9263</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H40" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M40">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="N40" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -2500,13 +2494,13 @@
         <v>65</v>
       </c>
       <c r="E42">
-        <v>29.071</v>
+        <v>29.07028</v>
       </c>
       <c r="F42">
-        <v>-80.9263</v>
+        <v>-80.9258</v>
       </c>
       <c r="G42">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H42" t="s">
         <v>97</v>
@@ -2620,71 +2614,74 @@
         <v>127</v>
       </c>
       <c r="M45">
-        <v>1</v>
-      </c>
-      <c r="N45" t="s">
-        <v>181</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="1">
-        <v>43137</v>
+        <v>43136</v>
       </c>
       <c r="B46" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C46" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E46">
-        <v>29.07028</v>
+        <v>29.66549</v>
       </c>
       <c r="F46">
-        <v>-80.9258</v>
+        <v>-85.3488</v>
       </c>
       <c r="G46">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H46" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I46" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="M46">
-        <v>17</v>
+        <v>1</v>
+      </c>
+      <c r="N46" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="1">
-        <v>43136</v>
+        <v>43137</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C47" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D47" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E47">
-        <v>29.66549</v>
+        <v>30.32741</v>
       </c>
       <c r="F47">
-        <v>-85.3488</v>
+        <v>-87.3137</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H47" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I47" t="s">
-        <v>124</v>
+        <v>128</v>
+      </c>
+      <c r="L47" t="s">
+        <v>146</v>
       </c>
       <c r="M47">
         <v>1</v>
@@ -2695,34 +2692,34 @@
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="1">
-        <v>43137</v>
+        <v>43144</v>
       </c>
       <c r="B48" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C48" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D48" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E48">
-        <v>30.32741</v>
+        <v>25.4792</v>
       </c>
       <c r="F48">
-        <v>-87.3137</v>
+        <v>-81.18680000000001</v>
       </c>
       <c r="G48">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H48" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I48" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L48" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M48">
         <v>1</v>
@@ -2763,10 +2760,7 @@
         <v>147</v>
       </c>
       <c r="M49">
-        <v>1</v>
-      </c>
-      <c r="N49" t="s">
-        <v>184</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:14">
@@ -2783,13 +2777,13 @@
         <v>68</v>
       </c>
       <c r="E50">
-        <v>25.4792</v>
+        <v>25.50993</v>
       </c>
       <c r="F50">
-        <v>-81.18680000000001</v>
+        <v>-81.20950000000001</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H50" t="s">
         <v>100</v>
@@ -2801,74 +2795,71 @@
         <v>147</v>
       </c>
       <c r="M50">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="1">
-        <v>43144</v>
+        <v>43139</v>
       </c>
       <c r="B51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C51" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D51" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E51">
-        <v>25.50993</v>
+        <v>30.410008</v>
       </c>
       <c r="F51">
-        <v>-81.20950000000001</v>
+        <v>-81.40774399999999</v>
       </c>
       <c r="G51">
         <v>3</v>
       </c>
       <c r="H51" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I51" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L51" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M51">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="1">
-        <v>43139</v>
+        <v>43137</v>
       </c>
       <c r="B52" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C52" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D52" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E52">
-        <v>30.410008</v>
+        <v>26.86351</v>
       </c>
       <c r="F52">
-        <v>-81.40774399999999</v>
+        <v>-80.0475</v>
       </c>
       <c r="G52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H52" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I52" t="s">
-        <v>130</v>
-      </c>
-      <c r="L52" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="M52">
         <v>1</v>
@@ -2876,31 +2867,31 @@
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="1">
-        <v>43137</v>
+        <v>43135</v>
       </c>
       <c r="B53" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C53" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D53" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E53">
-        <v>26.86351</v>
+        <v>26.6232</v>
       </c>
       <c r="F53">
-        <v>-80.0475</v>
+        <v>-80.0406</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H53" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I53" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M53">
         <v>1</v>
@@ -2908,34 +2899,37 @@
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="1">
-        <v>43135</v>
+        <v>43137</v>
       </c>
       <c r="B54" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C54" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D54" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E54">
-        <v>26.6232</v>
+        <v>29.87753</v>
       </c>
       <c r="F54">
-        <v>-80.0406</v>
+        <v>-84.5711</v>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H54" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I54" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M54">
         <v>1</v>
+      </c>
+      <c r="N54" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="55" spans="1:14">
@@ -2969,9 +2963,6 @@
       <c r="M55">
         <v>1</v>
       </c>
-      <c r="N55" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="1">
@@ -2987,13 +2978,13 @@
         <v>72</v>
       </c>
       <c r="E56">
-        <v>29.87753</v>
+        <v>29.87701</v>
       </c>
       <c r="F56">
-        <v>-84.5711</v>
+        <v>-84.5727</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H56" t="s">
         <v>104</v>
@@ -3004,6 +2995,9 @@
       <c r="M56">
         <v>1</v>
       </c>
+      <c r="N56" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="1">
@@ -3104,10 +3098,7 @@
         <v>133</v>
       </c>
       <c r="M59">
-        <v>1</v>
-      </c>
-      <c r="N59" t="s">
-        <v>188</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -3124,13 +3115,13 @@
         <v>72</v>
       </c>
       <c r="E60">
-        <v>29.87701</v>
+        <v>29.87547</v>
       </c>
       <c r="F60">
-        <v>-84.5727</v>
+        <v>-84.5741</v>
       </c>
       <c r="G60">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H60" t="s">
         <v>104</v>
@@ -3139,7 +3130,10 @@
         <v>133</v>
       </c>
       <c r="M60">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="N60" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -3171,10 +3165,7 @@
         <v>133</v>
       </c>
       <c r="M61">
-        <v>1</v>
-      </c>
-      <c r="N61" t="s">
-        <v>189</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -3191,13 +3182,13 @@
         <v>72</v>
       </c>
       <c r="E62">
-        <v>29.87547</v>
+        <v>29.8754</v>
       </c>
       <c r="F62">
-        <v>-84.5741</v>
+        <v>-84.57729999999999</v>
       </c>
       <c r="G62">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H62" t="s">
         <v>104</v>
@@ -3223,13 +3214,13 @@
         <v>72</v>
       </c>
       <c r="E63">
-        <v>29.8754</v>
+        <v>29.87467</v>
       </c>
       <c r="F63">
-        <v>-84.57729999999999</v>
+        <v>-84.5787</v>
       </c>
       <c r="G63">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H63" t="s">
         <v>104</v>
@@ -3238,7 +3229,10 @@
         <v>133</v>
       </c>
       <c r="M63">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="N63" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -3305,10 +3299,7 @@
         <v>133</v>
       </c>
       <c r="M65">
-        <v>1</v>
-      </c>
-      <c r="N65" t="s">
-        <v>191</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:14">
@@ -3316,31 +3307,37 @@
         <v>43137</v>
       </c>
       <c r="B66" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C66" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D66" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E66">
-        <v>29.87467</v>
+        <v>30.4847</v>
       </c>
       <c r="F66">
-        <v>-84.5787</v>
+        <v>-81.4153</v>
       </c>
       <c r="G66">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H66" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I66" t="s">
-        <v>133</v>
+        <v>123</v>
+      </c>
+      <c r="L66" t="s">
+        <v>149</v>
       </c>
       <c r="M66">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="N66" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -3603,10 +3600,7 @@
         <v>149</v>
       </c>
       <c r="M73">
-        <v>1</v>
-      </c>
-      <c r="N73" t="s">
-        <v>198</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74" spans="1:14">
@@ -3623,13 +3617,13 @@
         <v>73</v>
       </c>
       <c r="E74">
-        <v>30.4847</v>
+        <v>30.43977</v>
       </c>
       <c r="F74">
-        <v>-81.4153</v>
+        <v>-81.4081</v>
       </c>
       <c r="G74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H74" t="s">
         <v>105</v>
@@ -3641,7 +3635,10 @@
         <v>149</v>
       </c>
       <c r="M74">
-        <v>9</v>
+        <v>1</v>
+      </c>
+      <c r="N74" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="75" spans="1:14">
@@ -3676,10 +3673,7 @@
         <v>149</v>
       </c>
       <c r="M75">
-        <v>1</v>
-      </c>
-      <c r="N75" t="s">
-        <v>199</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:14">
@@ -3696,13 +3690,13 @@
         <v>73</v>
       </c>
       <c r="E76">
-        <v>30.43977</v>
+        <v>30.4329</v>
       </c>
       <c r="F76">
-        <v>-81.4081</v>
+        <v>-81.407</v>
       </c>
       <c r="G76">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H76" t="s">
         <v>105</v>
@@ -3714,7 +3708,7 @@
         <v>149</v>
       </c>
       <c r="M76">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:14">
@@ -3722,31 +3716,28 @@
         <v>43137</v>
       </c>
       <c r="B77" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C77" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D77" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E77">
-        <v>30.4329</v>
+        <v>24.80786</v>
       </c>
       <c r="F77">
-        <v>-81.407</v>
+        <v>-80.83499999999999</v>
       </c>
       <c r="G77">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H77" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="I77" t="s">
-        <v>123</v>
-      </c>
-      <c r="L77" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="M77">
         <v>1</v>
@@ -3766,13 +3757,13 @@
         <v>74</v>
       </c>
       <c r="E78">
-        <v>24.80786</v>
+        <v>24.80772</v>
       </c>
       <c r="F78">
-        <v>-80.83499999999999</v>
+        <v>-80.8355</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H78" t="s">
         <v>90</v>
@@ -3781,7 +3772,7 @@
         <v>120</v>
       </c>
       <c r="M78">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:14">
@@ -3789,31 +3780,34 @@
         <v>43137</v>
       </c>
       <c r="B79" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C79" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D79" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E79">
-        <v>24.80772</v>
+        <v>27.17168</v>
       </c>
       <c r="F79">
-        <v>-80.8355</v>
+        <v>-80.1833</v>
       </c>
       <c r="G79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H79" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="I79" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="M79">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="N79" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="80" spans="1:14">
@@ -3847,40 +3841,40 @@
       <c r="M80">
         <v>1</v>
       </c>
-      <c r="N80" t="s">
-        <v>200</v>
-      </c>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="1">
-        <v>43137</v>
+        <v>43138</v>
       </c>
       <c r="B81" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C81" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D81" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E81">
-        <v>27.17168</v>
+        <v>25.85589</v>
       </c>
       <c r="F81">
-        <v>-80.1833</v>
+        <v>-81.68340000000001</v>
       </c>
       <c r="G81">
         <v>1</v>
       </c>
       <c r="H81" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I81" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M81">
         <v>1</v>
+      </c>
+      <c r="N81" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="82" spans="1:14">
@@ -4017,42 +4011,36 @@
         <v>134</v>
       </c>
       <c r="M85">
-        <v>1</v>
-      </c>
-      <c r="N85" t="s">
-        <v>204</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="1">
-        <v>43138</v>
+        <v>43139</v>
       </c>
       <c r="B86" t="s">
-        <v>23</v>
-      </c>
-      <c r="C86" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D86" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E86">
-        <v>25.85589</v>
+        <v>27.43161</v>
       </c>
       <c r="F86">
-        <v>-81.68340000000001</v>
+        <v>-80.27630000000001</v>
       </c>
       <c r="G86">
         <v>1</v>
       </c>
       <c r="H86" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I86" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M86">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:14">
@@ -4066,13 +4054,13 @@
         <v>77</v>
       </c>
       <c r="E87">
-        <v>27.43161</v>
+        <v>27.43255</v>
       </c>
       <c r="F87">
-        <v>-80.27630000000001</v>
+        <v>-80.27670000000001</v>
       </c>
       <c r="G87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H87" t="s">
         <v>108</v>
@@ -4081,33 +4069,39 @@
         <v>135</v>
       </c>
       <c r="M87">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="N87" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="1">
-        <v>43139</v>
+        <v>43137</v>
       </c>
       <c r="B88" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="C88" t="s">
+        <v>42</v>
       </c>
       <c r="D88" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E88">
-        <v>27.43255</v>
+        <v>30.3858</v>
       </c>
       <c r="F88">
-        <v>-80.27670000000001</v>
+        <v>-86.8536</v>
       </c>
       <c r="G88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H88" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I88" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M88">
         <v>1</v>
@@ -4118,31 +4112,34 @@
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="1">
-        <v>43137</v>
+        <v>43134</v>
       </c>
       <c r="B89" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C89" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D89" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E89">
-        <v>30.3858</v>
+        <v>27.6495</v>
       </c>
       <c r="F89">
-        <v>-86.8536</v>
+        <v>-82.7501</v>
       </c>
       <c r="G89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H89" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I89" t="s">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="L89" t="s">
+        <v>150</v>
       </c>
       <c r="M89">
         <v>1</v>
@@ -4183,10 +4180,7 @@
         <v>150</v>
       </c>
       <c r="M90">
-        <v>1</v>
-      </c>
-      <c r="N90" t="s">
-        <v>207</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91" spans="1:14">
@@ -4194,34 +4188,37 @@
         <v>43134</v>
       </c>
       <c r="B91" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C91" t="s">
         <v>43</v>
       </c>
       <c r="D91" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E91">
-        <v>27.6495</v>
+        <v>27.6559</v>
       </c>
       <c r="F91">
-        <v>-82.7501</v>
+        <v>-82.7393</v>
       </c>
       <c r="G91">
         <v>2</v>
       </c>
       <c r="H91" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I91" t="s">
         <v>137</v>
       </c>
       <c r="L91" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M91">
-        <v>9</v>
+        <v>1</v>
+      </c>
+      <c r="N91" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="92" spans="1:14">
@@ -4258,9 +4255,6 @@
       <c r="M92">
         <v>1</v>
       </c>
-      <c r="N92" t="s">
-        <v>208</v>
-      </c>
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="1">
@@ -4276,13 +4270,13 @@
         <v>80</v>
       </c>
       <c r="E93">
-        <v>27.6559</v>
+        <v>27.6501</v>
       </c>
       <c r="F93">
-        <v>-82.7393</v>
+        <v>-82.7347</v>
       </c>
       <c r="G93">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H93" t="s">
         <v>111</v>
@@ -4295,6 +4289,9 @@
       </c>
       <c r="M93">
         <v>1</v>
+      </c>
+      <c r="N93" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="94" spans="1:14">
@@ -4329,15 +4326,12 @@
         <v>151</v>
       </c>
       <c r="M94">
-        <v>1</v>
-      </c>
-      <c r="N94" t="s">
-        <v>209</v>
+        <v>14</v>
       </c>
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="1">
-        <v>43134</v>
+        <v>43138</v>
       </c>
       <c r="B95" t="s">
         <v>34</v>
@@ -4346,28 +4340,28 @@
         <v>43</v>
       </c>
       <c r="D95" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E95">
-        <v>27.6501</v>
+        <v>29.63802</v>
       </c>
       <c r="F95">
-        <v>-82.7347</v>
+        <v>-85.148</v>
       </c>
       <c r="G95">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H95" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I95" t="s">
-        <v>137</v>
-      </c>
-      <c r="L95" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="M95">
-        <v>14</v>
+        <v>1</v>
+      </c>
+      <c r="N95" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="96" spans="1:14">
@@ -4401,40 +4395,40 @@
       <c r="M96">
         <v>1</v>
       </c>
-      <c r="N96" t="s">
-        <v>210</v>
-      </c>
     </row>
     <row r="97" spans="1:14">
       <c r="A97" s="1">
         <v>43138</v>
       </c>
       <c r="B97" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C97" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D97" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E97">
-        <v>29.63802</v>
+        <v>29.71343</v>
       </c>
       <c r="F97">
-        <v>-85.148</v>
+        <v>-84.7499</v>
       </c>
       <c r="G97">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H97" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I97" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M97">
         <v>1</v>
+      </c>
+      <c r="N97" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="98" spans="1:14">
@@ -4451,13 +4445,13 @@
         <v>82</v>
       </c>
       <c r="E98">
-        <v>29.71343</v>
+        <v>29.71624</v>
       </c>
       <c r="F98">
-        <v>-84.7499</v>
+        <v>-84.7466</v>
       </c>
       <c r="G98">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H98" t="s">
         <v>113</v>
@@ -4467,9 +4461,6 @@
       </c>
       <c r="M98">
         <v>1</v>
-      </c>
-      <c r="N98" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="99" spans="1:14">
@@ -4486,13 +4477,13 @@
         <v>82</v>
       </c>
       <c r="E99">
-        <v>29.71624</v>
+        <v>29.71831</v>
       </c>
       <c r="F99">
-        <v>-84.7466</v>
+        <v>-84.744</v>
       </c>
       <c r="G99">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H99" t="s">
         <v>113</v>
@@ -4502,6 +4493,9 @@
       </c>
       <c r="M99">
         <v>1</v>
+      </c>
+      <c r="N99" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="100" spans="1:14">
@@ -4518,13 +4512,13 @@
         <v>82</v>
       </c>
       <c r="E100">
-        <v>29.71831</v>
+        <v>29.73627</v>
       </c>
       <c r="F100">
-        <v>-84.744</v>
+        <v>-84.7229</v>
       </c>
       <c r="G100">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H100" t="s">
         <v>113</v>
@@ -4553,13 +4547,13 @@
         <v>82</v>
       </c>
       <c r="E101">
-        <v>29.73627</v>
+        <v>29.7464</v>
       </c>
       <c r="F101">
-        <v>-84.7229</v>
+        <v>-84.7123</v>
       </c>
       <c r="G101">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H101" t="s">
         <v>113</v>
@@ -4640,37 +4634,34 @@
       <c r="M103">
         <v>1</v>
       </c>
-      <c r="N103" t="s">
-        <v>215</v>
-      </c>
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="1">
-        <v>43138</v>
+        <v>43133</v>
       </c>
       <c r="B104" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C104" t="s">
         <v>47</v>
       </c>
       <c r="D104" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E104">
-        <v>29.7464</v>
+        <v>28.13208</v>
       </c>
       <c r="F104">
-        <v>-84.7123</v>
+        <v>-82.8282</v>
       </c>
       <c r="G104">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H104" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I104" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M104">
         <v>1</v>
@@ -4681,31 +4672,34 @@
         <v>43133</v>
       </c>
       <c r="B105" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C105" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D105" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E105">
-        <v>28.13208</v>
+        <v>28.11171</v>
       </c>
       <c r="F105">
-        <v>-82.8282</v>
+        <v>-82.837</v>
       </c>
       <c r="G105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H105" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I105" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M105">
         <v>1</v>
+      </c>
+      <c r="N105" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="106" spans="1:14">
@@ -4947,10 +4941,7 @@
         <v>141</v>
       </c>
       <c r="M112">
-        <v>1</v>
-      </c>
-      <c r="N112" t="s">
-        <v>222</v>
+        <v>22</v>
       </c>
     </row>
     <row r="113" spans="1:14">
@@ -4958,31 +4949,37 @@
         <v>43133</v>
       </c>
       <c r="B113" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C113" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D113" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E113">
-        <v>28.11171</v>
+        <v>30.06609</v>
       </c>
       <c r="F113">
-        <v>-82.837</v>
+        <v>-85.6161</v>
       </c>
       <c r="G113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H113" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="I113" t="s">
-        <v>141</v>
+        <v>117</v>
+      </c>
+      <c r="L113" t="s">
+        <v>152</v>
       </c>
       <c r="M113">
-        <v>22</v>
+        <v>1</v>
+      </c>
+      <c r="N113" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="114" spans="1:14">
@@ -5133,9 +5130,6 @@
       <c r="M117">
         <v>1</v>
       </c>
-      <c r="N117" t="s">
-        <v>226</v>
-      </c>
     </row>
     <row r="118" spans="1:14">
       <c r="A118" s="1">
@@ -5151,13 +5145,13 @@
         <v>85</v>
       </c>
       <c r="E118">
-        <v>30.06609</v>
+        <v>30.08727</v>
       </c>
       <c r="F118">
-        <v>-85.6161</v>
+        <v>-85.6602</v>
       </c>
       <c r="G118">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H118" t="s">
         <v>87</v>
@@ -5170,6 +5164,9 @@
       </c>
       <c r="M118">
         <v>1</v>
+      </c>
+      <c r="N118" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="119" spans="1:14">
@@ -5212,74 +5209,36 @@
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="1">
-        <v>43133</v>
+        <v>43137</v>
       </c>
       <c r="B120" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C120" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D120" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E120">
-        <v>30.08727</v>
+        <v>29.30722</v>
       </c>
       <c r="F120">
-        <v>-85.6602</v>
+        <v>-81.0467</v>
       </c>
       <c r="G120">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H120" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="I120" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="L120" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M120">
-        <v>1</v>
-      </c>
-      <c r="N120" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="121" spans="1:14">
-      <c r="A121" s="1">
-        <v>43137</v>
-      </c>
-      <c r="B121" t="s">
-        <v>39</v>
-      </c>
-      <c r="C121" t="s">
-        <v>43</v>
-      </c>
-      <c r="D121" t="s">
-        <v>86</v>
-      </c>
-      <c r="E121">
-        <v>29.30722</v>
-      </c>
-      <c r="F121">
-        <v>-81.0467</v>
-      </c>
-      <c r="G121">
-        <v>6</v>
-      </c>
-      <c r="H121" t="s">
-        <v>116</v>
-      </c>
-      <c r="I121" t="s">
-        <v>142</v>
-      </c>
-      <c r="L121" t="s">
-        <v>153</v>
-      </c>
-      <c r="M121">
         <v>2</v>
       </c>
     </row>

--- a/Databases/Database3/Output/2018/db3_2018_extracted.xlsx
+++ b/Databases/Database3/Output/2018/db3_2018_extracted.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="226">
   <si>
     <t>SurveyDate</t>
   </si>
@@ -460,9 +460,6 @@
     <t>End time was 13:45</t>
   </si>
   <si>
-    <t>GPS borrowed from 2024 — point 3 had no coordinates in 2018</t>
-  </si>
-  <si>
     <t>Sunny, fair weather, rising tide, low at 6:55 a.m.</t>
   </si>
   <si>
@@ -523,49 +520,46 @@
     <t>Yf(9C8)//WB:S//bO</t>
   </si>
   <si>
-    <t>X:X (not banded) 6 total for this point</t>
-  </si>
-  <si>
     <t>LL=FO,G/K RL=_,B</t>
   </si>
   <si>
-    <t>bf (missing) S, Y/G: -, G/K (photo; 5th winter)</t>
-  </si>
-  <si>
-    <t>Gf (5TH), -: O, - (photo; 3rd winter)</t>
-  </si>
-  <si>
-    <t>O (green dot), O/Y: S, - (photo; 3rd winter)</t>
-  </si>
-  <si>
-    <t>Gf (M9E), -: O, - (photo)</t>
-  </si>
-  <si>
-    <t>Yf (4Y?), -: S, - (photo)</t>
-  </si>
-  <si>
-    <t>PPI: (UL) FO, (LL) K/O/Y, (UR) S, (LR) Lb (reported to bander);</t>
-  </si>
-  <si>
-    <t>(UL) S, (LL) Y, (UR) -, (LR) O (reported to bander)</t>
-  </si>
-  <si>
-    <t>Band/Flag Code: HY: (UL) S, (LL) -, (UR) FK, (LR) -(reported);</t>
-  </si>
-  <si>
-    <t>(UL) S, (LL) B, (UR) FO, (LR) R/Y (reported);</t>
-  </si>
-  <si>
-    <t>Band/flag code: LMX: (UL) FG, (LL) -, (UR) B, (LR) - (reported)</t>
+    <t>bf (missing) S, Y/G: -, G/K</t>
+  </si>
+  <si>
+    <t>Gf (5TH), -: O, -</t>
+  </si>
+  <si>
+    <t>O (green dot), O/Y: S, -</t>
+  </si>
+  <si>
+    <t>Gf (M9E), -: O, -</t>
+  </si>
+  <si>
+    <t>Yf (4Y?), -: S, -</t>
+  </si>
+  <si>
+    <t>(UL) FO, (LL) K/O/Y, (UR) S, (LR) Lb</t>
+  </si>
+  <si>
+    <t>(UL) S, (LL) Y, (UR) -, (LR) O</t>
+  </si>
+  <si>
+    <t>(UL) S, (LL) -, (UR) FK, (LR) ;</t>
+  </si>
+  <si>
+    <t>(UL) S, (LL) B, (UR) FO, (LR) R/Y;</t>
+  </si>
+  <si>
+    <t>LMX: (UL) FG, (LL) -, (UR) B, (LR)</t>
   </si>
   <si>
     <t>S//:Bf(A97)//</t>
   </si>
   <si>
-    <t>S/LY:bf/LG (bf = light blue flag, no code); reported directly to bander</t>
-  </si>
-  <si>
-    <t>YX6, color: green, position: upper left". The "O" is for an orange band on the right leg, position: upper right.</t>
+    <t>S/LY:bf/LG</t>
+  </si>
+  <si>
+    <t>fg(YX6)/-:O/M</t>
   </si>
   <si>
     <t>S//BK:Bf(C63)//YB</t>
@@ -577,7 +571,7 @@
     <t>Yf(J87)//RO:S//YB</t>
   </si>
   <si>
-    <t>S//RY:Yf(E60)//YK- all reported to the banders</t>
+    <t>S//RY:Yf(E60)//YK</t>
   </si>
   <si>
     <t>Yf(6H1)//:S//</t>
@@ -610,37 +604,37 @@
     <t>FW[VA],_:S,_</t>
   </si>
   <si>
-    <t>Banded - FK[UN], _ : S, _</t>
-  </si>
-  <si>
-    <t>Left leg: Orange flag, upper yellow band, lower green band. Right leg: Upper silver USFWS band, lower Yellow band</t>
-  </si>
-  <si>
-    <t>fY(20E),BO:X,Rb continuing bird, will be batch reported at end of season.</t>
-  </si>
-  <si>
-    <t>G,-:fG(K5K),- continuing bird, will be batch reported at end of season.</t>
-  </si>
-  <si>
-    <t>X,-:fK(KT),- continuing bird, will be batch reported at end of season.</t>
-  </si>
-  <si>
-    <t>X,O/R:O(B.),R(125) reported to Great Lakes Plover coordinators</t>
-  </si>
-  <si>
-    <t>left-- green flag NLP, right-- blue band</t>
-  </si>
-  <si>
-    <t>Silver band//white : yellow flag//black</t>
-  </si>
-  <si>
-    <t>-, O : S, Y-O split band Reported to Great Lakes researchers</t>
-  </si>
-  <si>
-    <t>S, B-O split : O, B Reported to Great Lakes researcher</t>
-  </si>
-  <si>
-    <t>S, K : FO, B/Y FTP; Y; FTP, - : -, - reported to Great Lakes area researchers</t>
+    <t>FK[UN], _ : S, _</t>
+  </si>
+  <si>
+    <t>FO/OG:M/-</t>
+  </si>
+  <si>
+    <t>fY(20E),BO:X,Rb</t>
+  </si>
+  <si>
+    <t>G,-:fG(K5K)</t>
+  </si>
+  <si>
+    <t>X,-:fK(KT)</t>
+  </si>
+  <si>
+    <t>X,O/R:O(B.),R(125)</t>
+  </si>
+  <si>
+    <t>FG(NLP)/-:B/M</t>
+  </si>
+  <si>
+    <t>M/W:FY/N</t>
+  </si>
+  <si>
+    <t>-, O : S, Y-O</t>
+  </si>
+  <si>
+    <t>M/BO:O/B</t>
+  </si>
+  <si>
+    <t>S, K : FO, B/Y FTP</t>
   </si>
   <si>
     <t>S//x:YF(622)//x</t>
@@ -688,10 +682,10 @@
     <t>O(blue dot)//Y:S//Y/O</t>
   </si>
   <si>
-    <t>O//b:S//(missing band light blue, LR )</t>
-  </si>
-  <si>
-    <t>S//KY:Yf(H67)//W (missing band Red, LR)</t>
+    <t>O//b:S//</t>
+  </si>
+  <si>
+    <t>S//KY:Yf(H67)//W</t>
   </si>
   <si>
     <t>X//OG:Gf//KY</t>
@@ -1033,7 +1027,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N120"/>
+  <dimension ref="A1:N119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -1185,7 +1179,7 @@
         <v>1</v>
       </c>
       <c r="N4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1223,7 +1217,7 @@
         <v>1</v>
       </c>
       <c r="N5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1261,7 +1255,7 @@
         <v>1</v>
       </c>
       <c r="N6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1299,7 +1293,7 @@
         <v>1</v>
       </c>
       <c r="N7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1337,7 +1331,7 @@
         <v>1</v>
       </c>
       <c r="N8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1375,7 +1369,7 @@
         <v>1</v>
       </c>
       <c r="N9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1413,7 +1407,7 @@
         <v>1</v>
       </c>
       <c r="N10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1451,7 +1445,7 @@
         <v>1</v>
       </c>
       <c r="N11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1489,7 +1483,7 @@
         <v>1</v>
       </c>
       <c r="N12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1527,7 +1521,7 @@
         <v>1</v>
       </c>
       <c r="N13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1565,7 +1559,7 @@
         <v>1</v>
       </c>
       <c r="N14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1635,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="N16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1670,7 +1664,7 @@
         <v>1</v>
       </c>
       <c r="N17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1999,7 +1993,7 @@
         <v>1</v>
       </c>
       <c r="N27" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -2034,7 +2028,7 @@
         <v>1</v>
       </c>
       <c r="N28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -2066,10 +2060,7 @@
         <v>124</v>
       </c>
       <c r="M29">
-        <v>1</v>
-      </c>
-      <c r="N29" t="s">
-        <v>169</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -2077,31 +2068,34 @@
         <v>43133</v>
       </c>
       <c r="B30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E30">
-        <v>29.99092</v>
+        <v>28.05099</v>
       </c>
       <c r="F30">
-        <v>-85.502</v>
+        <v>-82.8197</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I30" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M30">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="N30" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -2133,42 +2127,42 @@
         <v>125</v>
       </c>
       <c r="M31">
-        <v>1</v>
-      </c>
-      <c r="N31" t="s">
-        <v>170</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="1">
-        <v>43133</v>
+        <v>43134</v>
       </c>
       <c r="B32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E32">
-        <v>28.05099</v>
+        <v>25.70076</v>
       </c>
       <c r="F32">
-        <v>-82.8197</v>
+        <v>-80.1549</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I32" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M32">
-        <v>27</v>
+        <v>1</v>
+      </c>
+      <c r="N32" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -2203,7 +2197,7 @@
         <v>1</v>
       </c>
       <c r="N33" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -2238,7 +2232,7 @@
         <v>1</v>
       </c>
       <c r="N34" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -2273,7 +2267,7 @@
         <v>1</v>
       </c>
       <c r="N35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:14">
@@ -2308,7 +2302,7 @@
         <v>1</v>
       </c>
       <c r="N36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="37" spans="1:14">
@@ -2340,10 +2334,7 @@
         <v>126</v>
       </c>
       <c r="M37">
-        <v>1</v>
-      </c>
-      <c r="N37" t="s">
-        <v>175</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:14">
@@ -2360,13 +2351,13 @@
         <v>64</v>
       </c>
       <c r="E38">
-        <v>25.70076</v>
+        <v>25.70171</v>
       </c>
       <c r="F38">
-        <v>-80.1549</v>
+        <v>-80.1544</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" t="s">
         <v>96</v>
@@ -2375,39 +2366,42 @@
         <v>126</v>
       </c>
       <c r="M38">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="1">
-        <v>43134</v>
+        <v>43137</v>
       </c>
       <c r="B39" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C39" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D39" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E39">
-        <v>25.70171</v>
+        <v>29.071</v>
       </c>
       <c r="F39">
-        <v>-80.1544</v>
+        <v>-80.9263</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H39" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I39" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M39">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="N39" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="40" spans="1:14">
@@ -2442,7 +2436,7 @@
         <v>1</v>
       </c>
       <c r="N40" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -2459,13 +2453,13 @@
         <v>65</v>
       </c>
       <c r="E41">
-        <v>29.071</v>
+        <v>29.07028</v>
       </c>
       <c r="F41">
-        <v>-80.9263</v>
+        <v>-80.9258</v>
       </c>
       <c r="G41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H41" t="s">
         <v>97</v>
@@ -2477,7 +2471,7 @@
         <v>1</v>
       </c>
       <c r="N41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="42" spans="1:14">
@@ -2512,7 +2506,7 @@
         <v>1</v>
       </c>
       <c r="N42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="43" spans="1:14">
@@ -2547,7 +2541,7 @@
         <v>1</v>
       </c>
       <c r="N43" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="44" spans="1:14">
@@ -2579,115 +2573,118 @@
         <v>127</v>
       </c>
       <c r="M44">
-        <v>1</v>
-      </c>
-      <c r="N44" t="s">
-        <v>180</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="1">
-        <v>43137</v>
+        <v>43136</v>
       </c>
       <c r="B45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C45" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D45" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E45">
-        <v>29.07028</v>
+        <v>29.66549</v>
       </c>
       <c r="F45">
-        <v>-80.9258</v>
+        <v>-85.3488</v>
       </c>
       <c r="G45">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H45" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I45" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="M45">
-        <v>17</v>
+        <v>1</v>
+      </c>
+      <c r="N45" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="1">
-        <v>43136</v>
+        <v>43137</v>
       </c>
       <c r="B46" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C46" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D46" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E46">
-        <v>29.66549</v>
+        <v>30.32741</v>
       </c>
       <c r="F46">
-        <v>-85.3488</v>
+        <v>-87.3137</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H46" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I46" t="s">
-        <v>124</v>
+        <v>128</v>
+      </c>
+      <c r="L46" t="s">
+        <v>146</v>
       </c>
       <c r="M46">
         <v>1</v>
       </c>
       <c r="N46" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="1">
-        <v>43137</v>
+        <v>43144</v>
       </c>
       <c r="B47" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C47" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D47" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E47">
-        <v>30.32741</v>
+        <v>25.4792</v>
       </c>
       <c r="F47">
-        <v>-87.3137</v>
+        <v>-81.18680000000001</v>
       </c>
       <c r="G47">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H47" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I47" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L47" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M47">
         <v>1</v>
       </c>
       <c r="N47" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="48" spans="1:14">
@@ -2722,10 +2719,7 @@
         <v>147</v>
       </c>
       <c r="M48">
-        <v>1</v>
-      </c>
-      <c r="N48" t="s">
-        <v>183</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:14">
@@ -2742,13 +2736,13 @@
         <v>68</v>
       </c>
       <c r="E49">
-        <v>25.4792</v>
+        <v>25.50993</v>
       </c>
       <c r="F49">
-        <v>-81.18680000000001</v>
+        <v>-81.20950000000001</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H49" t="s">
         <v>100</v>
@@ -2760,74 +2754,68 @@
         <v>147</v>
       </c>
       <c r="M49">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="1">
-        <v>43144</v>
+        <v>43139</v>
       </c>
       <c r="B50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C50" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E50">
-        <v>25.50993</v>
+        <v>30.410008</v>
       </c>
       <c r="F50">
-        <v>-81.20950000000001</v>
+        <v>-81.40774399999999</v>
       </c>
       <c r="G50">
         <v>3</v>
       </c>
       <c r="H50" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I50" t="s">
-        <v>129</v>
-      </c>
-      <c r="L50" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="M50">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="1">
-        <v>43139</v>
+        <v>43137</v>
       </c>
       <c r="B51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C51" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D51" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E51">
-        <v>30.410008</v>
+        <v>26.86351</v>
       </c>
       <c r="F51">
-        <v>-81.40774399999999</v>
+        <v>-80.0475</v>
       </c>
       <c r="G51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H51" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I51" t="s">
-        <v>130</v>
-      </c>
-      <c r="L51" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="M51">
         <v>1</v>
@@ -2835,31 +2823,31 @@
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="1">
-        <v>43137</v>
+        <v>43135</v>
       </c>
       <c r="B52" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C52" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E52">
-        <v>26.86351</v>
+        <v>26.6232</v>
       </c>
       <c r="F52">
-        <v>-80.0475</v>
+        <v>-80.0406</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H52" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I52" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M52">
         <v>1</v>
@@ -2867,34 +2855,37 @@
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="1">
-        <v>43135</v>
+        <v>43137</v>
       </c>
       <c r="B53" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C53" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D53" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E53">
-        <v>26.6232</v>
+        <v>29.87753</v>
       </c>
       <c r="F53">
-        <v>-80.0406</v>
+        <v>-84.5711</v>
       </c>
       <c r="G53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H53" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I53" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M53">
         <v>1</v>
+      </c>
+      <c r="N53" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="54" spans="1:14">
@@ -2928,9 +2919,6 @@
       <c r="M54">
         <v>1</v>
       </c>
-      <c r="N54" t="s">
-        <v>184</v>
-      </c>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="1">
@@ -2946,13 +2934,13 @@
         <v>72</v>
       </c>
       <c r="E55">
-        <v>29.87753</v>
+        <v>29.87701</v>
       </c>
       <c r="F55">
-        <v>-84.5711</v>
+        <v>-84.5727</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H55" t="s">
         <v>104</v>
@@ -2963,6 +2951,9 @@
       <c r="M55">
         <v>1</v>
       </c>
+      <c r="N55" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="1">
@@ -2996,7 +2987,7 @@
         <v>1</v>
       </c>
       <c r="N56" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="57" spans="1:14">
@@ -3031,7 +3022,7 @@
         <v>1</v>
       </c>
       <c r="N57" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="58" spans="1:14">
@@ -3063,10 +3054,7 @@
         <v>133</v>
       </c>
       <c r="M58">
-        <v>1</v>
-      </c>
-      <c r="N58" t="s">
-        <v>187</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:14">
@@ -3083,13 +3071,13 @@
         <v>72</v>
       </c>
       <c r="E59">
-        <v>29.87701</v>
+        <v>29.87547</v>
       </c>
       <c r="F59">
-        <v>-84.5727</v>
+        <v>-84.5741</v>
       </c>
       <c r="G59">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H59" t="s">
         <v>104</v>
@@ -3098,7 +3086,10 @@
         <v>133</v>
       </c>
       <c r="M59">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="N59" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -3130,10 +3121,7 @@
         <v>133</v>
       </c>
       <c r="M60">
-        <v>1</v>
-      </c>
-      <c r="N60" t="s">
-        <v>188</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -3150,13 +3138,13 @@
         <v>72</v>
       </c>
       <c r="E61">
-        <v>29.87547</v>
+        <v>29.8754</v>
       </c>
       <c r="F61">
-        <v>-84.5741</v>
+        <v>-84.57729999999999</v>
       </c>
       <c r="G61">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H61" t="s">
         <v>104</v>
@@ -3182,13 +3170,13 @@
         <v>72</v>
       </c>
       <c r="E62">
-        <v>29.8754</v>
+        <v>29.87467</v>
       </c>
       <c r="F62">
-        <v>-84.57729999999999</v>
+        <v>-84.5787</v>
       </c>
       <c r="G62">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H62" t="s">
         <v>104</v>
@@ -3197,7 +3185,10 @@
         <v>133</v>
       </c>
       <c r="M62">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="N62" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="63" spans="1:14">
@@ -3232,7 +3223,7 @@
         <v>1</v>
       </c>
       <c r="N63" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -3264,10 +3255,7 @@
         <v>133</v>
       </c>
       <c r="M64">
-        <v>1</v>
-      </c>
-      <c r="N64" t="s">
-        <v>190</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:14">
@@ -3275,31 +3263,37 @@
         <v>43137</v>
       </c>
       <c r="B65" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C65" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D65" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E65">
-        <v>29.87467</v>
+        <v>30.4847</v>
       </c>
       <c r="F65">
-        <v>-84.5787</v>
+        <v>-81.4153</v>
       </c>
       <c r="G65">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H65" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I65" t="s">
-        <v>133</v>
+        <v>123</v>
+      </c>
+      <c r="L65" t="s">
+        <v>148</v>
       </c>
       <c r="M65">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="N65" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="66" spans="1:14">
@@ -3331,13 +3325,13 @@
         <v>123</v>
       </c>
       <c r="L66" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M66">
         <v>1</v>
       </c>
       <c r="N66" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -3369,13 +3363,13 @@
         <v>123</v>
       </c>
       <c r="L67" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M67">
         <v>1</v>
       </c>
       <c r="N67" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="68" spans="1:14">
@@ -3407,13 +3401,13 @@
         <v>123</v>
       </c>
       <c r="L68" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M68">
         <v>1</v>
       </c>
       <c r="N68" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="69" spans="1:14">
@@ -3445,13 +3439,13 @@
         <v>123</v>
       </c>
       <c r="L69" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M69">
         <v>1</v>
       </c>
       <c r="N69" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="70" spans="1:14">
@@ -3483,13 +3477,13 @@
         <v>123</v>
       </c>
       <c r="L70" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M70">
         <v>1</v>
       </c>
       <c r="N70" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="71" spans="1:14">
@@ -3521,13 +3515,13 @@
         <v>123</v>
       </c>
       <c r="L71" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M71">
         <v>1</v>
       </c>
       <c r="N71" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="72" spans="1:14">
@@ -3559,13 +3553,10 @@
         <v>123</v>
       </c>
       <c r="L72" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M72">
-        <v>1</v>
-      </c>
-      <c r="N72" t="s">
-        <v>197</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:14">
@@ -3582,13 +3573,13 @@
         <v>73</v>
       </c>
       <c r="E73">
-        <v>30.4847</v>
+        <v>30.43977</v>
       </c>
       <c r="F73">
-        <v>-81.4153</v>
+        <v>-81.4081</v>
       </c>
       <c r="G73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H73" t="s">
         <v>105</v>
@@ -3597,10 +3588,13 @@
         <v>123</v>
       </c>
       <c r="L73" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M73">
-        <v>9</v>
+        <v>1</v>
+      </c>
+      <c r="N73" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="74" spans="1:14">
@@ -3632,13 +3626,10 @@
         <v>123</v>
       </c>
       <c r="L74" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M74">
-        <v>1</v>
-      </c>
-      <c r="N74" t="s">
-        <v>198</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:14">
@@ -3655,13 +3646,13 @@
         <v>73</v>
       </c>
       <c r="E75">
-        <v>30.43977</v>
+        <v>30.4329</v>
       </c>
       <c r="F75">
-        <v>-81.4081</v>
+        <v>-81.407</v>
       </c>
       <c r="G75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H75" t="s">
         <v>105</v>
@@ -3670,10 +3661,10 @@
         <v>123</v>
       </c>
       <c r="L75" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M75">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:14">
@@ -3681,31 +3672,28 @@
         <v>43137</v>
       </c>
       <c r="B76" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C76" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D76" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E76">
-        <v>30.4329</v>
+        <v>24.80786</v>
       </c>
       <c r="F76">
-        <v>-81.407</v>
+        <v>-80.83499999999999</v>
       </c>
       <c r="G76">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H76" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="I76" t="s">
-        <v>123</v>
-      </c>
-      <c r="L76" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="M76">
         <v>1</v>
@@ -3725,13 +3713,13 @@
         <v>74</v>
       </c>
       <c r="E77">
-        <v>24.80786</v>
+        <v>24.80772</v>
       </c>
       <c r="F77">
-        <v>-80.83499999999999</v>
+        <v>-80.8355</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H77" t="s">
         <v>90</v>
@@ -3740,7 +3728,7 @@
         <v>120</v>
       </c>
       <c r="M77">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:14">
@@ -3748,31 +3736,34 @@
         <v>43137</v>
       </c>
       <c r="B78" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C78" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D78" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E78">
-        <v>24.80772</v>
+        <v>27.17168</v>
       </c>
       <c r="F78">
-        <v>-80.8355</v>
+        <v>-80.1833</v>
       </c>
       <c r="G78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="I78" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="M78">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="N78" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="79" spans="1:14">
@@ -3806,40 +3797,40 @@
       <c r="M79">
         <v>1</v>
       </c>
-      <c r="N79" t="s">
-        <v>199</v>
-      </c>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="1">
-        <v>43137</v>
+        <v>43138</v>
       </c>
       <c r="B80" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C80" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D80" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E80">
-        <v>27.17168</v>
+        <v>25.85589</v>
       </c>
       <c r="F80">
-        <v>-80.1833</v>
+        <v>-81.68340000000001</v>
       </c>
       <c r="G80">
         <v>1</v>
       </c>
       <c r="H80" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I80" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M80">
         <v>1</v>
+      </c>
+      <c r="N80" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="81" spans="1:14">
@@ -3874,7 +3865,7 @@
         <v>1</v>
       </c>
       <c r="N81" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:14">
@@ -3909,7 +3900,7 @@
         <v>1</v>
       </c>
       <c r="N82" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="83" spans="1:14">
@@ -3944,7 +3935,7 @@
         <v>1</v>
       </c>
       <c r="N83" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="84" spans="1:14">
@@ -3976,42 +3967,36 @@
         <v>134</v>
       </c>
       <c r="M84">
-        <v>1</v>
-      </c>
-      <c r="N84" t="s">
-        <v>203</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="1">
-        <v>43138</v>
+        <v>43139</v>
       </c>
       <c r="B85" t="s">
-        <v>23</v>
-      </c>
-      <c r="C85" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D85" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E85">
-        <v>25.85589</v>
+        <v>27.43161</v>
       </c>
       <c r="F85">
-        <v>-81.68340000000001</v>
+        <v>-80.27630000000001</v>
       </c>
       <c r="G85">
         <v>1</v>
       </c>
       <c r="H85" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I85" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M85">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:14">
@@ -4025,13 +4010,13 @@
         <v>77</v>
       </c>
       <c r="E86">
-        <v>27.43161</v>
+        <v>27.43255</v>
       </c>
       <c r="F86">
-        <v>-80.27630000000001</v>
+        <v>-80.27670000000001</v>
       </c>
       <c r="G86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H86" t="s">
         <v>108</v>
@@ -4040,74 +4025,83 @@
         <v>135</v>
       </c>
       <c r="M86">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="N86" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="1">
-        <v>43139</v>
+        <v>43137</v>
       </c>
       <c r="B87" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="C87" t="s">
+        <v>42</v>
       </c>
       <c r="D87" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E87">
-        <v>27.43255</v>
+        <v>30.3858</v>
       </c>
       <c r="F87">
-        <v>-80.27670000000001</v>
+        <v>-86.8536</v>
       </c>
       <c r="G87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H87" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I87" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M87">
         <v>1</v>
       </c>
       <c r="N87" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="1">
-        <v>43137</v>
+        <v>43134</v>
       </c>
       <c r="B88" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C88" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D88" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E88">
-        <v>30.3858</v>
+        <v>27.6495</v>
       </c>
       <c r="F88">
-        <v>-86.8536</v>
+        <v>-82.7501</v>
       </c>
       <c r="G88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H88" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I88" t="s">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="L88" t="s">
+        <v>149</v>
       </c>
       <c r="M88">
         <v>1</v>
       </c>
       <c r="N88" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="89" spans="1:14">
@@ -4139,13 +4133,10 @@
         <v>137</v>
       </c>
       <c r="L89" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M89">
-        <v>1</v>
-      </c>
-      <c r="N89" t="s">
-        <v>206</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90" spans="1:14">
@@ -4153,25 +4144,25 @@
         <v>43134</v>
       </c>
       <c r="B90" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C90" t="s">
         <v>43</v>
       </c>
       <c r="D90" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E90">
-        <v>27.6495</v>
+        <v>27.6559</v>
       </c>
       <c r="F90">
-        <v>-82.7501</v>
+        <v>-82.7393</v>
       </c>
       <c r="G90">
         <v>2</v>
       </c>
       <c r="H90" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I90" t="s">
         <v>137</v>
@@ -4180,7 +4171,10 @@
         <v>150</v>
       </c>
       <c r="M90">
-        <v>9</v>
+        <v>1</v>
+      </c>
+      <c r="N90" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="91" spans="1:14">
@@ -4212,13 +4206,10 @@
         <v>137</v>
       </c>
       <c r="L91" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M91">
         <v>1</v>
-      </c>
-      <c r="N91" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="92" spans="1:14">
@@ -4235,13 +4226,13 @@
         <v>80</v>
       </c>
       <c r="E92">
-        <v>27.6559</v>
+        <v>27.6501</v>
       </c>
       <c r="F92">
-        <v>-82.7393</v>
+        <v>-82.7347</v>
       </c>
       <c r="G92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H92" t="s">
         <v>111</v>
@@ -4250,10 +4241,13 @@
         <v>137</v>
       </c>
       <c r="L92" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M92">
         <v>1</v>
+      </c>
+      <c r="N92" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="93" spans="1:14">
@@ -4285,18 +4279,15 @@
         <v>137</v>
       </c>
       <c r="L93" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M93">
-        <v>1</v>
-      </c>
-      <c r="N93" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
     </row>
     <row r="94" spans="1:14">
       <c r="A94" s="1">
-        <v>43134</v>
+        <v>43138</v>
       </c>
       <c r="B94" t="s">
         <v>34</v>
@@ -4305,28 +4296,28 @@
         <v>43</v>
       </c>
       <c r="D94" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E94">
-        <v>27.6501</v>
+        <v>29.63802</v>
       </c>
       <c r="F94">
-        <v>-82.7347</v>
+        <v>-85.148</v>
       </c>
       <c r="G94">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H94" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I94" t="s">
-        <v>137</v>
-      </c>
-      <c r="L94" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="M94">
-        <v>14</v>
+        <v>1</v>
+      </c>
+      <c r="N94" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="95" spans="1:14">
@@ -4360,40 +4351,40 @@
       <c r="M95">
         <v>1</v>
       </c>
-      <c r="N95" t="s">
-        <v>209</v>
-      </c>
     </row>
     <row r="96" spans="1:14">
       <c r="A96" s="1">
         <v>43138</v>
       </c>
       <c r="B96" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C96" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D96" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E96">
-        <v>29.63802</v>
+        <v>29.71343</v>
       </c>
       <c r="F96">
-        <v>-85.148</v>
+        <v>-84.7499</v>
       </c>
       <c r="G96">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H96" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I96" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M96">
         <v>1</v>
+      </c>
+      <c r="N96" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="97" spans="1:14">
@@ -4410,13 +4401,13 @@
         <v>82</v>
       </c>
       <c r="E97">
-        <v>29.71343</v>
+        <v>29.71624</v>
       </c>
       <c r="F97">
-        <v>-84.7499</v>
+        <v>-84.7466</v>
       </c>
       <c r="G97">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H97" t="s">
         <v>113</v>
@@ -4426,9 +4417,6 @@
       </c>
       <c r="M97">
         <v>1</v>
-      </c>
-      <c r="N97" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="98" spans="1:14">
@@ -4445,13 +4433,13 @@
         <v>82</v>
       </c>
       <c r="E98">
-        <v>29.71624</v>
+        <v>29.71831</v>
       </c>
       <c r="F98">
-        <v>-84.7466</v>
+        <v>-84.744</v>
       </c>
       <c r="G98">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H98" t="s">
         <v>113</v>
@@ -4461,6 +4449,9 @@
       </c>
       <c r="M98">
         <v>1</v>
+      </c>
+      <c r="N98" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="99" spans="1:14">
@@ -4477,13 +4468,13 @@
         <v>82</v>
       </c>
       <c r="E99">
-        <v>29.71831</v>
+        <v>29.73627</v>
       </c>
       <c r="F99">
-        <v>-84.744</v>
+        <v>-84.7229</v>
       </c>
       <c r="G99">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H99" t="s">
         <v>113</v>
@@ -4495,7 +4486,7 @@
         <v>1</v>
       </c>
       <c r="N99" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="100" spans="1:14">
@@ -4512,13 +4503,13 @@
         <v>82</v>
       </c>
       <c r="E100">
-        <v>29.73627</v>
+        <v>29.7464</v>
       </c>
       <c r="F100">
-        <v>-84.7229</v>
+        <v>-84.7123</v>
       </c>
       <c r="G100">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H100" t="s">
         <v>113</v>
@@ -4530,7 +4521,7 @@
         <v>1</v>
       </c>
       <c r="N100" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="101" spans="1:14">
@@ -4565,7 +4556,7 @@
         <v>1</v>
       </c>
       <c r="N101" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="102" spans="1:14">
@@ -4599,37 +4590,34 @@
       <c r="M102">
         <v>1</v>
       </c>
-      <c r="N102" t="s">
-        <v>214</v>
-      </c>
     </row>
     <row r="103" spans="1:14">
       <c r="A103" s="1">
-        <v>43138</v>
+        <v>43133</v>
       </c>
       <c r="B103" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C103" t="s">
         <v>47</v>
       </c>
       <c r="D103" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E103">
-        <v>29.7464</v>
+        <v>28.13208</v>
       </c>
       <c r="F103">
-        <v>-84.7123</v>
+        <v>-82.8282</v>
       </c>
       <c r="G103">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H103" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I103" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M103">
         <v>1</v>
@@ -4640,31 +4628,34 @@
         <v>43133</v>
       </c>
       <c r="B104" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C104" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D104" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E104">
-        <v>28.13208</v>
+        <v>28.11171</v>
       </c>
       <c r="F104">
-        <v>-82.8282</v>
+        <v>-82.837</v>
       </c>
       <c r="G104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H104" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I104" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M104">
         <v>1</v>
+      </c>
+      <c r="N104" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="105" spans="1:14">
@@ -4699,7 +4690,7 @@
         <v>1</v>
       </c>
       <c r="N105" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="106" spans="1:14">
@@ -4734,7 +4725,7 @@
         <v>1</v>
       </c>
       <c r="N106" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="107" spans="1:14">
@@ -4769,7 +4760,7 @@
         <v>1</v>
       </c>
       <c r="N107" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="108" spans="1:14">
@@ -4804,7 +4795,7 @@
         <v>1</v>
       </c>
       <c r="N108" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="109" spans="1:14">
@@ -4839,7 +4830,7 @@
         <v>1</v>
       </c>
       <c r="N109" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="110" spans="1:14">
@@ -4874,7 +4865,7 @@
         <v>1</v>
       </c>
       <c r="N110" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="111" spans="1:14">
@@ -4906,10 +4897,7 @@
         <v>141</v>
       </c>
       <c r="M111">
-        <v>1</v>
-      </c>
-      <c r="N111" t="s">
-        <v>221</v>
+        <v>22</v>
       </c>
     </row>
     <row r="112" spans="1:14">
@@ -4917,31 +4905,37 @@
         <v>43133</v>
       </c>
       <c r="B112" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C112" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D112" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E112">
-        <v>28.11171</v>
+        <v>30.06609</v>
       </c>
       <c r="F112">
-        <v>-82.837</v>
+        <v>-85.6161</v>
       </c>
       <c r="G112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H112" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="I112" t="s">
-        <v>141</v>
+        <v>117</v>
+      </c>
+      <c r="L112" t="s">
+        <v>151</v>
       </c>
       <c r="M112">
-        <v>22</v>
+        <v>1</v>
+      </c>
+      <c r="N112" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="113" spans="1:14">
@@ -4973,13 +4967,13 @@
         <v>117</v>
       </c>
       <c r="L113" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M113">
         <v>1</v>
       </c>
       <c r="N113" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="114" spans="1:14">
@@ -5011,13 +5005,13 @@
         <v>117</v>
       </c>
       <c r="L114" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M114">
         <v>1</v>
       </c>
       <c r="N114" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="115" spans="1:14">
@@ -5049,13 +5043,13 @@
         <v>117</v>
       </c>
       <c r="L115" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M115">
         <v>1</v>
       </c>
       <c r="N115" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="116" spans="1:14">
@@ -5087,13 +5081,10 @@
         <v>117</v>
       </c>
       <c r="L116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M116">
         <v>1</v>
-      </c>
-      <c r="N116" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="117" spans="1:14">
@@ -5110,13 +5101,13 @@
         <v>85</v>
       </c>
       <c r="E117">
-        <v>30.06609</v>
+        <v>30.08727</v>
       </c>
       <c r="F117">
-        <v>-85.6161</v>
+        <v>-85.6602</v>
       </c>
       <c r="G117">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H117" t="s">
         <v>87</v>
@@ -5125,10 +5116,13 @@
         <v>117</v>
       </c>
       <c r="L117" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M117">
         <v>1</v>
+      </c>
+      <c r="N117" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="118" spans="1:14">
@@ -5160,85 +5154,47 @@
         <v>117</v>
       </c>
       <c r="L118" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M118">
         <v>1</v>
       </c>
       <c r="N118" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="119" spans="1:14">
       <c r="A119" s="1">
-        <v>43133</v>
+        <v>43137</v>
       </c>
       <c r="B119" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C119" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D119" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E119">
-        <v>30.08727</v>
+        <v>29.30722</v>
       </c>
       <c r="F119">
-        <v>-85.6602</v>
+        <v>-81.0467</v>
       </c>
       <c r="G119">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H119" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="I119" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="L119" t="s">
         <v>152</v>
       </c>
       <c r="M119">
-        <v>1</v>
-      </c>
-      <c r="N119" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="120" spans="1:14">
-      <c r="A120" s="1">
-        <v>43137</v>
-      </c>
-      <c r="B120" t="s">
-        <v>39</v>
-      </c>
-      <c r="C120" t="s">
-        <v>43</v>
-      </c>
-      <c r="D120" t="s">
-        <v>86</v>
-      </c>
-      <c r="E120">
-        <v>29.30722</v>
-      </c>
-      <c r="F120">
-        <v>-81.0467</v>
-      </c>
-      <c r="G120">
-        <v>6</v>
-      </c>
-      <c r="H120" t="s">
-        <v>116</v>
-      </c>
-      <c r="I120" t="s">
-        <v>142</v>
-      </c>
-      <c r="L120" t="s">
-        <v>153</v>
-      </c>
-      <c r="M120">
         <v>2</v>
       </c>
     </row>
